--- a/algo_2.xlsx
+++ b/algo_2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>frozenset({'vehicle_type_involved_No Heavy Vehicle Involved', 'holiday_NoHoliday', 'time_of_day_Night', 'lga_name_nan'})</t>
+          <t>frozenset({'vehicle_type_involved_No Heavy Vehicle Involved', 'time_of_day_Night', 'holiday_type_NoHoliday', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>frozenset({'holiday_NoHoliday', 'time_cat_Not Rush', 'lga_name_nan'})</t>
+          <t>frozenset({'holiday_type_NoHoliday', 'time_cat_Not Rush', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -599,49 +599,49 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'speed_limit_Very High', 'time_of_day_Night', 'holiday_NoHoliday'})</t>
+          <t>frozenset({'vehicle_type_involved_No Heavy Vehicle Involved', 'speed_limit_Very High', 'time_of_day_Night', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>frozenset({'time_cat_Not Rush', 'lga_name_nan'})</t>
+          <t>frozenset({'road_type_nan', 'time_cat_Not Rush', 'holiday_type_NoHoliday'})</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1506136371628512</v>
+        <v>0.06899461968562084</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6822097970953336</v>
+        <v>0.6582093751098921</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1452509055104265</v>
+        <v>0.0642121180152618</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9643941162736398</v>
+        <v>0.9306829765545361</v>
       </c>
       <c r="G4" t="n">
-        <v>1.413632756931623</v>
+        <v>1.413961896849544</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04250080666176762</v>
+        <v>0.01879921250604465</v>
       </c>
       <c r="J4" t="n">
-        <v>8.925215993709376</v>
+        <v>4.930832397311701</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3444871610611154</v>
+        <v>0.314463664599164</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2112517580872011</v>
+        <v>0.09685204338716949</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8879578936011392</v>
+        <v>0.7971944857535206</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5886532437038302</v>
+        <v>0.5141193699388147</v>
       </c>
     </row>
     <row r="5">
@@ -839,7 +839,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'holiday_NoHoliday', 'state_NSW', 'time_of_day_Night'})</t>
+          <t>frozenset({'road_type_nan', 'time_of_day_Night', 'state_NSW', 'holiday_type_NoHoliday'})</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -887,7 +887,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>frozenset({'holiday_NoHoliday', 'state_NSW', 'time_of_day_Night', 'lga_name_nan'})</t>
+          <t>frozenset({'holiday_type_NoHoliday', 'time_of_day_Night', 'state_NSW', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>frozenset({'holiday_NoHoliday', 'time_cat_Not Rush', 'lga_name_nan'})</t>
+          <t>frozenset({'holiday_type_NoHoliday', 'time_cat_Not Rush', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -988,7 +988,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'holiday_NoHoliday', 'time_cat_Not Rush'})</t>
+          <t>frozenset({'road_type_nan', 'time_cat_Not Rush', 'holiday_type_NoHoliday'})</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1031,7 +1031,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>frozenset({'state_NSW', 'speed_limit_High', 'holiday_NoHoliday', 'time_cat_Not Rush', 'lga_name_nan'})</t>
+          <t>frozenset({'state_NSW', 'speed_limit_High', 'time_cat_Not Rush', 'lga_name_nan', 'holiday_type_NoHoliday'})</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>frozenset({'state_NSW', 'holiday_NoHoliday', 'time_of_day_Night', 'vehicle_type_involved_nan', 'lga_name_nan'})</t>
+          <t>frozenset({'state_NSW', 'time_of_day_Night', 'vehicle_type_involved_nan', 'lga_name_nan', 'holiday_type_NoHoliday'})</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>frozenset({'holiday_NoHoliday', 'time_cat_Not Rush', 'lga_name_nan'})</t>
+          <t>frozenset({'holiday_type_NoHoliday', 'time_cat_Not Rush', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1175,97 +1175,97 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>frozenset({'holiday_NoHoliday', 'state_NSW', 'time_of_day_Night', 'vehicle_type_involved_nan'})</t>
+          <t>frozenset({'time_of_day_Night', 'state_NSW', 'vehicle_type_involved_nan', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'time_cat_Not Rush', 'lga_name_nan'})</t>
+          <t>frozenset({'road_type_nan', 'time_cat_Not Rush', 'holiday_type_NoHoliday'})</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.05288884200161761</v>
+        <v>0.0547526110349193</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6814537398459753</v>
+        <v>0.6582093751098921</v>
       </c>
       <c r="E16" t="n">
         <v>0.05197454021169603</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9827127659574467</v>
+        <v>0.9492614001284521</v>
       </c>
       <c r="G16" t="n">
-        <v>1.442082871508729</v>
+        <v>1.442187601733821</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01593324103357081</v>
+        <v>0.01593585831676682</v>
       </c>
       <c r="J16" t="n">
-        <v>18.42667597198657</v>
+        <v>6.736303834859457</v>
       </c>
       <c r="K16" t="n">
-        <v>0.323677504348861</v>
+        <v>0.3243689816716605</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07616789919863949</v>
+        <v>0.07863166014949591</v>
       </c>
       <c r="M16" t="n">
-        <v>0.945730852296949</v>
+        <v>0.851550638968341</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5294914295509555</v>
+        <v>0.5141124684627836</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>frozenset({'time_of_day_Night', 'state_NSW', 'vehicle_type_involved_nan', 'lga_name_nan'})</t>
+          <t>frozenset({'holiday_type_NoHoliday', 'time_of_day_Night', 'state_NSW', 'vehicle_type_involved_nan'})</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'holiday_NoHoliday', 'time_cat_Not Rush'})</t>
+          <t>frozenset({'road_type_nan', 'time_cat_Not Rush', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0547526110349193</v>
+        <v>0.05288884200161761</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6582093751098921</v>
+        <v>0.6814537398459753</v>
       </c>
       <c r="E17" t="n">
         <v>0.05197454021169603</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9492614001284521</v>
+        <v>0.9827127659574467</v>
       </c>
       <c r="G17" t="n">
-        <v>1.442187601733821</v>
+        <v>1.442082871508729</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01593585831676682</v>
+        <v>0.01593324103357081</v>
       </c>
       <c r="J17" t="n">
-        <v>6.736303834859457</v>
+        <v>18.42667597198657</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3243689816716605</v>
+        <v>0.323677504348861</v>
       </c>
       <c r="L17" t="n">
-        <v>0.07863166014949591</v>
+        <v>0.07616789919863949</v>
       </c>
       <c r="M17" t="n">
-        <v>0.851550638968341</v>
+        <v>0.945730852296949</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5141124684627836</v>
+        <v>0.5294914295509555</v>
       </c>
     </row>
     <row r="18">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'holiday_NoHoliday', 'time_cat_Not Rush', 'lga_name_nan'})</t>
+          <t>frozenset({'road_type_nan', 'time_cat_Not Rush', 'holiday_type_NoHoliday', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1415,19 +1415,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>frozenset({'speed_limit_Very High', 'time_of_day_Night', 'holiday_NoHoliday', 'vehicle_type_involved_nan', 'lga_name_nan'})</t>
+          <t>frozenset({'speed_limit_Very High', 'road_type_nan', 'time_of_day_Night', 'vehicle_type_involved_nan', 'holiday_type_NoHoliday'})</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'time_cat_Not Rush'})</t>
+          <t>frozenset({'time_cat_Not Rush', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>0.05644055280092837</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6865175651440025</v>
+        <v>0.6822097970953336</v>
       </c>
       <c r="E21" t="n">
         <v>0.05445370468052185</v>
@@ -1436,412 +1436,412 @@
         <v>0.9647975077881619</v>
       </c>
       <c r="G21" t="n">
-        <v>1.405350069354435</v>
+        <v>1.414224058194431</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0.015706273796247</v>
+        <v>0.01594940660625205</v>
       </c>
       <c r="J21" t="n">
-        <v>8.905120494581844</v>
+        <v>9.027491604636952</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3056866446436998</v>
+        <v>0.3104186679012466</v>
       </c>
       <c r="L21" t="n">
-        <v>0.07908984115634096</v>
+        <v>0.07958779842212112</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8877050568143989</v>
+        <v>0.8892272578258226</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5220581212906746</v>
+        <v>0.5223085477085139</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'speed_limit_Very High', 'time_of_day_Night', 'vehicle_type_involved_nan'})</t>
+          <t>frozenset({'speed_limit_Very High', 'time_of_day_Night', 'vehicle_type_involved_nan', 'lga_name_nan', 'holiday_type_NoHoliday'})</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>frozenset({'holiday_NoHoliday', 'time_cat_Not Rush', 'lga_name_nan'})</t>
+          <t>frozenset({'road_type_nan', 'time_cat_Not Rush'})</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.05840981819460562</v>
+        <v>0.05644055280092837</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6540774343285156</v>
+        <v>0.6865175651440025</v>
       </c>
       <c r="E22" t="n">
         <v>0.05445370468052185</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9322697170379289</v>
+        <v>0.9647975077881619</v>
       </c>
       <c r="G22" t="n">
-        <v>1.425320104484279</v>
+        <v>1.405350069354435</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.01624916065619916</v>
+        <v>0.015706273796247</v>
       </c>
       <c r="J22" t="n">
-        <v>5.107354502936315</v>
+        <v>8.905120494581844</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3169141127447855</v>
+        <v>0.3056866446436998</v>
       </c>
       <c r="L22" t="n">
-        <v>0.08275217100868404</v>
+        <v>0.07908984115634096</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8042039182075414</v>
+        <v>0.8877050568143989</v>
       </c>
       <c r="N22" t="n">
-        <v>0.507761202604986</v>
+        <v>0.5220581212906746</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>frozenset({'speed_limit_Very High', 'time_of_day_Night', 'vehicle_type_involved_nan', 'holiday_NoHoliday'})</t>
+          <t>frozenset({'road_type_nan', 'speed_limit_Very High', 'time_of_day_Night', 'vehicle_type_involved_nan'})</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'time_cat_Not Rush', 'lga_name_nan'})</t>
+          <t>frozenset({'holiday_type_NoHoliday', 'time_cat_Not Rush', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.05649330098111615</v>
+        <v>0.05840981819460562</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6814537398459753</v>
+        <v>0.6540774343285156</v>
       </c>
       <c r="E23" t="n">
         <v>0.05445370468052185</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9638966697790227</v>
+        <v>0.9322697170379289</v>
       </c>
       <c r="G23" t="n">
-        <v>1.414471171582221</v>
+        <v>1.425320104484279</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01595613345069594</v>
+        <v>0.01624916065619916</v>
       </c>
       <c r="J23" t="n">
-        <v>8.823182188576549</v>
+        <v>5.107354502936315</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3105669522689158</v>
+        <v>0.3169141127447855</v>
       </c>
       <c r="L23" t="n">
-        <v>0.07966969361767808</v>
+        <v>0.08275217100868404</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8866622066022043</v>
+        <v>0.8042039182075414</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5219024077021646</v>
+        <v>0.507761202604986</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'time_of_day_Night', 'speed_limit_High', 'vehicle_type_involved_nan'})</t>
+          <t>frozenset({'speed_limit_Very High', 'time_of_day_Night', 'vehicle_type_involved_nan', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>frozenset({'time_cat_Not Rush', 'lga_name_nan'})</t>
+          <t>frozenset({'road_type_nan', 'time_cat_Not Rush', 'holiday_type_NoHoliday'})</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.07449801315187959</v>
+        <v>0.05840981819460562</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6822097970953336</v>
+        <v>0.6582093751098921</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07164961142173928</v>
+        <v>0.05445370468052185</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9617654000472032</v>
+        <v>0.9322697170379289</v>
       </c>
       <c r="G24" t="n">
-        <v>1.409779519646511</v>
+        <v>1.416372589470153</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0.02082633698539001</v>
+        <v>0.01600781474636808</v>
       </c>
       <c r="J24" t="n">
-        <v>8.311586973500447</v>
+        <v>5.046348692821947</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3140665591198707</v>
+        <v>0.3122070434692091</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1045890868025255</v>
+        <v>0.08223579394583111</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8796860331019496</v>
+        <v>0.801836919945222</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5333955866215397</v>
+        <v>0.5074998912423516</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>frozenset({'time_of_day_Night', 'speed_limit_High', 'vehicle_type_involved_nan', 'lga_name_nan'})</t>
+          <t>frozenset({'road_type_nan', 'time_of_day_Night', 'speed_limit_High', 'vehicle_type_involved_nan'})</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'time_cat_Not Rush'})</t>
+          <t>frozenset({'time_cat_Not Rush', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.07453317860533812</v>
+        <v>0.07449801315187959</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6865175651440025</v>
+        <v>0.6822097970953336</v>
       </c>
       <c r="E25" t="n">
         <v>0.07164961142173928</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9613116301014391</v>
+        <v>0.9617654000472032</v>
       </c>
       <c r="G25" t="n">
-        <v>1.400272445905731</v>
+        <v>1.409779519646511</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0204812751231595</v>
+        <v>0.02082633698539001</v>
       </c>
       <c r="J25" t="n">
-        <v>8.102756349723014</v>
+        <v>8.311586973500447</v>
       </c>
       <c r="K25" t="n">
-        <v>0.308874672839517</v>
+        <v>0.3140665591198707</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1039302201025275</v>
+        <v>0.1045890868025255</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8765852067075688</v>
+        <v>0.8796860331019496</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5328391932041323</v>
+        <v>0.5333955866215397</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>frozenset({'time_of_day_Night', 'speed_limit_High', 'vehicle_type_involved_nan'})</t>
+          <t>frozenset({'time_of_day_Night', 'speed_limit_High', 'vehicle_type_involved_nan', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'time_cat_Not Rush', 'lga_name_nan'})</t>
+          <t>frozenset({'road_type_nan', 'time_cat_Not Rush'})</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.07462109223898442</v>
+        <v>0.07453317860533812</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6814537398459753</v>
+        <v>0.6865175651440025</v>
       </c>
       <c r="E26" t="n">
         <v>0.07164961142173928</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9601790763430726</v>
+        <v>0.9613116301014391</v>
       </c>
       <c r="G26" t="n">
-        <v>1.409015785224241</v>
+        <v>1.400272445905731</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0.02079878904409187</v>
+        <v>0.0204812751231595</v>
       </c>
       <c r="J26" t="n">
-        <v>7.999469397004042</v>
+        <v>8.102756349723014</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3136928458774009</v>
+        <v>0.308874672839517</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1046858141088219</v>
+        <v>0.1039302201025275</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8749917087782698</v>
+        <v>0.8765852067075688</v>
       </c>
       <c r="N26" t="n">
-        <v>0.5326606866092379</v>
+        <v>0.5328391932041323</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>frozenset({'state_Vic'})</t>
+          <t>frozenset({'time_of_day_Night', 'speed_limit_High', 'vehicle_type_involved_nan'})</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>frozenset({'vehicle_type_involved_No Heavy Vehicle Involved', 'holiday_NoHoliday', 'lga_name_nan'})</t>
+          <t>frozenset({'road_type_nan', 'time_cat_Not Rush', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.218658789605092</v>
+        <v>0.07462109223898442</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3596019270668495</v>
+        <v>0.6814537398459753</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1459366318528677</v>
+        <v>0.07164961142173928</v>
       </c>
       <c r="F27" t="n">
-        <v>0.667417175940817</v>
+        <v>0.9601790763430726</v>
       </c>
       <c r="G27" t="n">
-        <v>1.855988874655683</v>
+        <v>1.409015785224241</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0.06730650974077186</v>
+        <v>0.02079878904409187</v>
       </c>
       <c r="J27" t="n">
-        <v>1.925529602271919</v>
+        <v>7.999469397004042</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5902717797695124</v>
+        <v>0.3136928458774009</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3375630388807548</v>
+        <v>0.1046858141088219</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4806623596853008</v>
+        <v>0.8749917087782698</v>
       </c>
       <c r="N27" t="n">
-        <v>0.5366227283967726</v>
+        <v>0.5326606866092379</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'holiday_NoHoliday', 'state_Vic', 'lga_name_nan'})</t>
+          <t>frozenset({'state_Vic'})</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>frozenset({'vehicle_type_involved_No Heavy Vehicle Involved'})</t>
+          <t>frozenset({'vehicle_type_involved_No Heavy Vehicle Involved', 'holiday_type_NoHoliday', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1682139466188416</v>
+        <v>0.218658789605092</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5361676688820902</v>
+        <v>0.3596019270668495</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1452509055104265</v>
+        <v>0.1459366318528677</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8634890770356433</v>
+        <v>0.667417175940817</v>
       </c>
       <c r="G28" t="n">
-        <v>1.610483300561592</v>
+        <v>1.855988874655683</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0.05506002587834585</v>
+        <v>0.06730650974077186</v>
       </c>
       <c r="J28" t="n">
-        <v>3.397767160647044</v>
+        <v>1.925529602271919</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4557282265553622</v>
+        <v>0.5902717797695124</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2597798742138364</v>
+        <v>0.3375630388807548</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7056890738182402</v>
+        <v>0.4806623596853008</v>
       </c>
       <c r="N28" t="n">
-        <v>0.5671974144934234</v>
+        <v>0.5366227283967726</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'holiday_NoHoliday', 'state_Vic'})</t>
+          <t>frozenset({'road_type_nan', 'state_Vic', 'holiday_type_NoHoliday', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>frozenset({'vehicle_type_involved_No Heavy Vehicle Involved', 'lga_name_nan'})</t>
+          <t>frozenset({'vehicle_type_involved_No Heavy Vehicle Involved'})</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.1732250237366811</v>
+        <v>0.1682139466188416</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3749868129549531</v>
+        <v>0.5361676688820902</v>
       </c>
       <c r="E29" t="n">
         <v>0.1452509055104265</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8385099472188388</v>
+        <v>0.8634890770356433</v>
       </c>
       <c r="G29" t="n">
-        <v>2.236105159568821</v>
+        <v>1.610483300561592</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0.08029380593536241</v>
+        <v>0.05506002587834585</v>
       </c>
       <c r="J29" t="n">
-        <v>3.870289075278316</v>
+        <v>3.397767160647044</v>
       </c>
       <c r="K29" t="n">
-        <v>0.668614625092543</v>
+        <v>0.4557282265553622</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3604590278383802</v>
+        <v>0.2597798742138364</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7416213671512148</v>
+        <v>0.7056890738182402</v>
       </c>
       <c r="N29" t="n">
-        <v>0.6129296582814314</v>
+        <v>0.5671974144934234</v>
       </c>
     </row>
     <row r="30">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>frozenset({'vehicle_type_involved_No Heavy Vehicle Involved', 'holiday_NoHoliday'})</t>
+          <t>frozenset({'vehicle_type_involved_No Heavy Vehicle Involved', 'holiday_type_NoHoliday'})</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1895,145 +1895,145 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>frozenset({'holiday_NoHoliday', 'state_Vic', 'lga_name_nan'})</t>
+          <t>frozenset({'road_type_nan', 'state_Vic', 'holiday_type_NoHoliday'})</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'vehicle_type_involved_No Heavy Vehicle Involved'})</t>
+          <t>frozenset({'vehicle_type_involved_No Heavy Vehicle Involved', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.1690579175018462</v>
+        <v>0.1732250237366811</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3793297464570806</v>
+        <v>0.3749868129549531</v>
       </c>
       <c r="E31" t="n">
         <v>0.1452509055104265</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8591783671346854</v>
+        <v>0.8385099472188388</v>
       </c>
       <c r="G31" t="n">
-        <v>2.264990750552429</v>
+        <v>2.236105159568821</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0.08112220852788919</v>
+        <v>0.08029380593536241</v>
       </c>
       <c r="J31" t="n">
-        <v>4.407492236200275</v>
+        <v>3.870289075278316</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6721251758349505</v>
+        <v>0.668614625092543</v>
       </c>
       <c r="L31" t="n">
-        <v>0.3603018143754361</v>
+        <v>0.3604590278383802</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7731136105500879</v>
+        <v>0.7416213671512148</v>
       </c>
       <c r="N31" t="n">
-        <v>0.6210464932920112</v>
+        <v>0.6129296582814314</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'state_Vic'})</t>
+          <t>frozenset({'holiday_type_NoHoliday', 'state_Vic', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>frozenset({'vehicle_type_involved_No Heavy Vehicle Involved', 'holiday_NoHoliday', 'lga_name_nan'})</t>
+          <t>frozenset({'road_type_nan', 'vehicle_type_involved_No Heavy Vehicle Involved'})</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1799592080739881</v>
+        <v>0.1690579175018462</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3596019270668495</v>
+        <v>0.3793297464570806</v>
       </c>
       <c r="E32" t="n">
         <v>0.1452509055104265</v>
       </c>
       <c r="F32" t="n">
-        <v>0.8071323888617489</v>
+        <v>0.8591783671346854</v>
       </c>
       <c r="G32" t="n">
-        <v>2.244516305697394</v>
+        <v>2.264990750552429</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0.08053722749359628</v>
+        <v>0.08112220852788919</v>
       </c>
       <c r="J32" t="n">
-        <v>3.320402369032823</v>
+        <v>4.407492236200275</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6761489376147922</v>
+        <v>0.6721251758349505</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3683670739320432</v>
+        <v>0.3603018143754361</v>
       </c>
       <c r="M32" t="n">
-        <v>0.6988316809654359</v>
+        <v>0.7731136105500879</v>
       </c>
       <c r="N32" t="n">
-        <v>0.6055268828721027</v>
+        <v>0.6210464932920112</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>frozenset({'holiday_NoHoliday', 'state_Vic'})</t>
+          <t>frozenset({'road_type_nan', 'state_Vic'})</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'vehicle_type_involved_No Heavy Vehicle Involved', 'lga_name_nan'})</t>
+          <t>frozenset({'vehicle_type_involved_No Heavy Vehicle Involved', 'holiday_type_NoHoliday', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.2101663325948588</v>
+        <v>0.1799592080739881</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3742483384323241</v>
+        <v>0.3596019270668495</v>
       </c>
       <c r="E33" t="n">
         <v>0.1452509055104265</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6911235673052789</v>
+        <v>0.8071323888617489</v>
       </c>
       <c r="G33" t="n">
-        <v>1.846697757431075</v>
+        <v>2.244516305697394</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.06659650474238545</v>
+        <v>0.08053722749359628</v>
       </c>
       <c r="J33" t="n">
-        <v>2.025896427605208</v>
+        <v>3.320402369032823</v>
       </c>
       <c r="K33" t="n">
-        <v>0.580492944693467</v>
+        <v>0.6761489376147922</v>
       </c>
       <c r="L33" t="n">
-        <v>0.3307442847419625</v>
+        <v>0.3683670739320432</v>
       </c>
       <c r="M33" t="n">
-        <v>0.5063913503307323</v>
+        <v>0.6988316809654359</v>
       </c>
       <c r="N33" t="n">
-        <v>0.539618631197859</v>
+        <v>0.6055268828721027</v>
       </c>
     </row>
     <row r="34">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'holiday_NoHoliday', 'vehicle_type_involved_No Heavy Vehicle Involved'})</t>
+          <t>frozenset({'road_type_nan', 'vehicle_type_involved_No Heavy Vehicle Involved', 'holiday_type_NoHoliday'})</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2087,96 +2087,144 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>frozenset({'state_Vic'})</t>
+          <t>frozenset({'holiday_type_NoHoliday', 'state_Vic'})</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>frozenset({'road_type_nan', 'holiday_NoHoliday', 'vehicle_type_involved_No Heavy Vehicle Involved', 'lga_name_nan'})</t>
+          <t>frozenset({'road_type_nan', 'vehicle_type_involved_No Heavy Vehicle Involved', 'lga_name_nan'})</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.218658789605092</v>
+        <v>0.2101663325948588</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3588634525442206</v>
+        <v>0.3742483384323241</v>
       </c>
       <c r="E35" t="n">
         <v>0.1452509055104265</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6642811193309746</v>
+        <v>0.6911235673052789</v>
       </c>
       <c r="G35" t="n">
-        <v>1.851069298423804</v>
+        <v>1.846697757431075</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.06678225734360291</v>
+        <v>0.06659650474238545</v>
       </c>
       <c r="J35" t="n">
-        <v>1.909742300397622</v>
+        <v>2.025896427605208</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5884390901612339</v>
+        <v>0.580492944693467</v>
       </c>
       <c r="L35" t="n">
-        <v>0.3360178970917225</v>
+        <v>0.3307442847419625</v>
       </c>
       <c r="M35" t="n">
-        <v>0.4763691416418891</v>
+        <v>0.5063913503307323</v>
       </c>
       <c r="N35" t="n">
-        <v>0.5345168457997351</v>
+        <v>0.539618631197859</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>frozenset({'state_Vic'})</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>frozenset({'road_type_nan', 'vehicle_type_involved_No Heavy Vehicle Involved', 'holiday_type_NoHoliday', 'lga_name_nan'})</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.218658789605092</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.3588634525442206</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.1452509055104265</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.6642811193309746</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.851069298423804</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.06678225734360291</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.909742300397622</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.5884390901612339</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.3360178970917225</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.4763691416418891</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.5345168457997351</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>frozenset({'state_Vic', 'time_of_day_Day'})</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>frozenset({'vehicle_type_involved_No Heavy Vehicle Involved'})</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C37" t="n">
         <v>0.1224812743960333</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D37" t="n">
         <v>0.5361676688820902</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E37" t="n">
         <v>0.1010127650596054</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F37" t="n">
         <v>0.8247200689061155</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G37" t="n">
         <v>1.538175680427835</v>
       </c>
-      <c r="H36" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" t="n">
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.03534226568497661</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J37" t="n">
         <v>2.646237525444194</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K37" t="n">
         <v>0.398714229482509</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L37" t="n">
         <v>0.1811445688160177</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M37" t="n">
         <v>0.6221049734255653</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N37" t="n">
         <v>0.5065588932449512</v>
       </c>
     </row>
